--- a/data/cholesterol.xlsx
+++ b/data/cholesterol.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\practical_stats_med-r\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My_R\bookdown-crc-master-draft\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E005F8-6E14-44E0-9049-7B09AFD1EBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A310B233-B5F2-4AC8-97D3-C8A388B55F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,9 +573,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -613,7 +613,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -719,7 +719,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -861,7 +861,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -869,7 +869,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -927,160 +927,6 @@
         <v>4.1500000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>8.43</v>
-      </c>
-      <c r="B6">
-        <v>7.71</v>
-      </c>
-      <c r="C6">
-        <v>7.67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>7.49</v>
-      </c>
-      <c r="B7">
-        <v>7.12</v>
-      </c>
-      <c r="C7">
-        <v>7.05</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>8.0500000000000007</v>
-      </c>
-      <c r="B8">
-        <v>7.25</v>
-      </c>
-      <c r="C8">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>5.05</v>
-      </c>
-      <c r="B9">
-        <v>4.63</v>
-      </c>
-      <c r="C9">
-        <v>4.67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>5.77</v>
-      </c>
-      <c r="B10">
-        <v>5.31</v>
-      </c>
-      <c r="C10">
-        <v>5.33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>3.91</v>
-      </c>
-      <c r="B11">
-        <v>3.7</v>
-      </c>
-      <c r="C11">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>6.77</v>
-      </c>
-      <c r="B12">
-        <v>6.15</v>
-      </c>
-      <c r="C12">
-        <v>5.96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>6.44</v>
-      </c>
-      <c r="B13">
-        <v>5.59</v>
-      </c>
-      <c r="C13">
-        <v>5.64</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>6.17</v>
-      </c>
-      <c r="B14">
-        <v>5.56</v>
-      </c>
-      <c r="C14">
-        <v>5.51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>7.67</v>
-      </c>
-      <c r="B15">
-        <v>7.11</v>
-      </c>
-      <c r="C15">
-        <v>6.96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>7.34</v>
-      </c>
-      <c r="B16">
-        <v>6.84</v>
-      </c>
-      <c r="C16">
-        <v>6.82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>6.85</v>
-      </c>
-      <c r="B17">
-        <v>6.4</v>
-      </c>
-      <c r="C17">
-        <v>6.29</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>5.13</v>
-      </c>
-      <c r="B18">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="C18">
-        <v>4.45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>5.73</v>
-      </c>
-      <c r="B19">
-        <v>5.13</v>
-      </c>
-      <c r="C19">
-        <v>5.17</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
